--- a/data/trans_orig/IP15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25622</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>42347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37497</t>
+          <t>37424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51261</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>73229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>96379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113104</t>
+          <t>113207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115580</t>
+          <t>115653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131643</t>
+          <t>131302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218760</t>
+          <t>218574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240542</t>
+          <t>241540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33432</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51093</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32015</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>51416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>70169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>96145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144070</t>
+          <t>143888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161731</t>
+          <t>162576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161022</t>
+          <t>160726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180127</t>
+          <t>179236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>312165</t>
+          <t>311160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336037</t>
+          <t>337136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>32992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43557</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49796</t>
+          <t>49730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72359</t>
+          <t>71064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104678</t>
+          <t>104825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119130</t>
+          <t>118565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106100</t>
+          <t>105574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122676</t>
+          <t>122521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215115</t>
+          <t>216410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237678</t>
+          <t>237744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>34822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48549</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>53397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76821</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175478</t>
+          <t>174493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190962</t>
+          <t>191144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159275</t>
+          <t>158392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177549</t>
+          <t>177286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340318</t>
+          <t>339840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364149</t>
+          <t>363742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110980</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142532</t>
+          <t>142934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>127498</t>
+          <t>127646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161419</t>
+          <t>162371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245290</t>
+          <t>246620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292494</t>
+          <t>293691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538489</t>
+          <t>538087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>570041</t>
+          <t>570569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561281</t>
+          <t>560329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>595202</t>
+          <t>595054</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1111227</t>
+          <t>1110030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1158431</t>
+          <t>1157101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>41410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44267</t>
+          <t>43873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>55021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79280</t>
+          <t>79399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>97947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115586</t>
+          <t>115232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110417</t>
+          <t>110811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>127922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214761</t>
+          <t>214642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239130</t>
+          <t>239020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51747</t>
+          <t>51685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31881</t>
+          <t>31626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50781</t>
+          <t>50175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69276</t>
+          <t>69413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96157</t>
+          <t>95513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154611</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173851</t>
+          <t>172935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173054</t>
+          <t>173660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191954</t>
+          <t>192209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334036</t>
+          <t>334680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360917</t>
+          <t>360780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>26041</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41887</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29015</t>
+          <t>28620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45461</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59635</t>
+          <t>58348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82745</t>
+          <t>83209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113489</t>
+          <t>113692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129525</t>
+          <t>129335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121131</t>
+          <t>120581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137577</t>
+          <t>137972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239223</t>
+          <t>238759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262333</t>
+          <t>263620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51879</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,82 +3724,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>25,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37303</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>58458</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>28,25%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>89015</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>74446</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>102910</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>21,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>24,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36687</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58272</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>89015</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>74205</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>102339</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158421</t>
+          <t>157357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178749</t>
+          <t>176998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,82 +3837,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>74,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>159668</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>148439</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>169594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>77,17%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>71,75%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>81,97%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>328182</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>314287</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>342751</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>78,66%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>75,33%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>159668</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>148625</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>170210</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>71,84%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>82,27%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>328182</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>314858</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>342992</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>78,66%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130280</t>
+          <t>130633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167322</t>
+          <t>166963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140344</t>
+          <t>140740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177591</t>
+          <t>177977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>281654</t>
+          <t>279624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>332147</t>
+          <t>331255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544069</t>
+          <t>544428</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>581111</t>
+          <t>580758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>574417</t>
+          <t>574031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>611664</t>
+          <t>611268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1131252</t>
+          <t>1132144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1181745</t>
+          <t>1183775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17420</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32556</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37764</t>
+          <t>38616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60431</t>
+          <t>60158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100795</t>
+          <t>100469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116287</t>
+          <t>116141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115520</t>
+          <t>114932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131124</t>
+          <t>130790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221352</t>
+          <t>221625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244019</t>
+          <t>243167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33166</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>51559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51232</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71293</t>
+          <t>72421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97469</t>
+          <t>97467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155398</t>
+          <t>155688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174081</t>
+          <t>173045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173127</t>
+          <t>172685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191946</t>
+          <t>192042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334137</t>
+          <t>334139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360313</t>
+          <t>359185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>44947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67609</t>
+          <t>66925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120167</t>
+          <t>120741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135115</t>
+          <t>135432</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129596</t>
+          <t>129602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145832</t>
+          <t>146180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255061</t>
+          <t>255745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276686</t>
+          <t>277723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39622</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51603</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76081</t>
+          <t>76673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164997</t>
+          <t>165047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183442</t>
+          <t>183134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166114</t>
+          <t>166465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182640</t>
+          <t>183608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337075</t>
+          <t>336483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>361553</t>
+          <t>361579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111129</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107274</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142274</t>
+          <t>141931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228851</t>
+          <t>227717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273319</t>
+          <t>273513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>559487</t>
+          <t>560662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>593242</t>
+          <t>593128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>602570</t>
+          <t>602913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>637570</t>
+          <t>636759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175896</t>
+          <t>1175702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220364</t>
+          <t>1221498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19082</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38085</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42028</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67142</t>
+          <t>66570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83269</t>
+          <t>82615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98160</t>
+          <t>97278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102327</t>
+          <t>102612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121330</t>
+          <t>121291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190551</t>
+          <t>191123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215665</t>
+          <t>215788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60127</t>
+          <t>60861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>51700</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
+          <t>76998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92989</t>
+          <t>92273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129280</t>
+          <t>128242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130385</t>
+          <t>129651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156605</t>
+          <t>156999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177246</t>
+          <t>177330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>201608</t>
+          <t>202628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315561</t>
+          <t>316599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351852</t>
+          <t>352568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53986</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115287</t>
+          <t>118431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45957</t>
+          <t>44587</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73137</t>
+          <t>70521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109171</t>
+          <t>110008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187674</t>
+          <t>185016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132100</t>
+          <t>130744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112149</t>
+          <t>114765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>140699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183698</t>
+          <t>186356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262201</t>
+          <t>261364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>53060</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77531</t>
+          <t>77008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129129</t>
+          <t>128793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144742</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137480</t>
+          <t>136498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156017</t>
+          <t>155453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271670</t>
+          <t>272193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296201</t>
+          <t>296141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148523</t>
+          <t>147455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>256457</t>
+          <t>245221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162543</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206332</t>
+          <t>206571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323800</t>
+          <t>324265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>435188</t>
+          <t>426090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405384</t>
+          <t>416620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>513318</t>
+          <t>514386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554933</t>
+          <t>554694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>598722</t>
+          <t>601233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>987918</t>
+          <t>997016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1099306</t>
+          <t>1098841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21507</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37185</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25519</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42347</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25211</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>41703</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21775</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37424</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,73%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>51849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73229</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124403</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>115892</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>131570</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105908</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>96379</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>113207</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>113515</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124403</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>115653</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>131302</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,27%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218574</t>
+          <t>217263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241540</t>
+          <t>239954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32883</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50353</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>32587</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>51275</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>33035</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>50854</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>32906</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>51416</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70169</t>
+          <t>71017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96145</t>
+          <t>95645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>170836</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>161789</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>179259</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>153516</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>143888</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>162576</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>144309</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>162128</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>170836</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>160726</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>179236</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>311160</t>
+          <t>311660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337136</t>
+          <t>336288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27649</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44398</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19252</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18477</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>32762</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27136</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>44083</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49730</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114534</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105259</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122008</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>70,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>81,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>112653</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>104825</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>118565</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>105055</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>119340</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>114534</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>105574</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>122521</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,53%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>216410</t>
+          <t>215915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237744</t>
+          <t>237817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30782</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48554</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18171</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34822</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17958</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34263</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30538</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>49432</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53397</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77299</t>
+          <t>76772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>169007</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>159270</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177042</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>183638</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>174493</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>191144</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>175052</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>191357</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>169007</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>158392</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177286</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>339840</t>
+          <t>340367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>363742</t>
+          <t>364296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,107 +2095,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>127434</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>163024</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>110452</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>142934</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>109450</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>141613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>127646</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>162371</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>16,07%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>247844</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>292802</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>17,66%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>269224</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>246620</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>293691</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2208,107 +2208,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>578781</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>559676</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>595266</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>828</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>555716</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>538087</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>570569</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>539408</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>571571</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>578781</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>560329</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>595054</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>83,93%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1699</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1134497</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1110919</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1155877</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>80,82%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>82,34%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1699</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1134497</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1110030</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1157101</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>80,82%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25539</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43095</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24125</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41410</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22498</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40196</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22,57%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26762</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>43873</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55021</t>
+          <t>54816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79399</t>
+          <t>79382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120260</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>111589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>129145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>77,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>107911</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97947</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115232</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>99161</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>116859</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>77,43%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>120260</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>110811</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>127922</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,75%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214642</t>
+          <t>214659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239020</t>
+          <t>239225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31653</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50872</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>41504</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33423</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>51685</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>32578</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>50714</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>31626</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>50175</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>67686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95513</t>
+          <t>95142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>183515</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>172963</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>192182</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>164854</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>154673</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>172935</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>155644</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>173780</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>183515</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>173660</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>192209</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,99%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334680</t>
+          <t>335051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>360780</t>
+          <t>362507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29131</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46076</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26041</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41684</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25942</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41961</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>28620</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46011</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58348</t>
+          <t>58862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83209</t>
+          <t>82115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>129991</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120516</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>137461</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122412</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113692</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129335</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113415</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>129434</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>129991</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>120581</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>137972</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,03%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238759</t>
+          <t>239853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263620</t>
+          <t>263106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37998</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>57031</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33302</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52943</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32481</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>52330</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37303</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58458</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74446</t>
+          <t>75194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102910</t>
+          <t>104709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159668</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149866</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>168899</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>168514</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157357</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>176998</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>157970</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>177819</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>159668</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>148439</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>169594</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314287</t>
+          <t>312488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342751</t>
+          <t>342003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206897</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206897</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206897</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206897</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206897</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206897</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>139830</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>176392</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>130633</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>166963</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>129929</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>165279</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>140740</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>177977</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>279624</t>
+          <t>280503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>331255</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>593434</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>575616</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>612178</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>78,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>81,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>812</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>563690</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>544428</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>580758</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>546112</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>581462</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>849</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>593434</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>574031</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>611268</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1132144</t>
+          <t>1130891</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183775</t>
+          <t>1182896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17192</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33090</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17566</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33238</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17950</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33351</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17286</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33144</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38616</t>
+          <t>37816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60158</t>
+          <t>59723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123900</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114986</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>130884</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>109348</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100469</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116141</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100356</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>115757</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>123900</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>114932</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>130790</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221625</t>
+          <t>222060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243167</t>
+          <t>243967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32397</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50473</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>34202</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>51559</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>33790</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>51745</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>32317</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>51674</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72421</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97467</t>
+          <t>97973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>183212</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>173886</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>191962</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>164548</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>155688</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>173045</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>155502</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>173457</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>183212</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>172685</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>192042</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334139</t>
+          <t>333633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359185</t>
+          <t>360368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20752</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36298</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20565</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35256</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21094</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35818</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20493</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>37071</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44947</t>
+          <t>45986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66925</t>
+          <t>67968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138867</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130375</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145921</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>128382</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120741</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135432</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>120179</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134903</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,3%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>138867</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>129602</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146180</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255745</t>
+          <t>254702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277723</t>
+          <t>276684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21729</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39215</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24286</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>42373</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24983</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>43717</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22128</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39271</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51577</t>
+          <t>50451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76673</t>
+          <t>75114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175590</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>166521</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>184007</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>174632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>165047</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>183134</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>163703</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>182437</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>175590</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>166465</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>183608</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336483</t>
+          <t>338042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>361579</t>
+          <t>362705</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>106791</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140198</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111243</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>143709</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>110759</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>144834</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>108085</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>141931</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227717</t>
+          <t>226261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273513</t>
+          <t>274110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>621568</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>604646</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>638053</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>869</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>576910</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>560662</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>593128</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>559537</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>593612</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>621568</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>602913</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>636759</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175702</t>
+          <t>1175105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1221498</t>
+          <t>1222954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16613</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32822</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20002</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34665</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>40236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66570</t>
+          <t>61929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>101284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93084</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>109293</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>91439</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82615</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>97278</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>77,97%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>112752</t>
+          <t>94763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102612</t>
+          <t>86839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121291</t>
+          <t>101526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>204192</t>
+          <t>196048</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191123</t>
+          <t>185048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215788</t>
+          <t>206741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45598</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68627</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33513</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60861</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23,22%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51700</t>
+          <t>27696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76998</t>
+          <t>45710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92593</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92273</t>
+          <t>79668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128242</t>
+          <t>110232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>180132</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>167963</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>190992</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>146270</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>129651</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>156999</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>190519</t>
+          <t>148277</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177330</t>
+          <t>138703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202628</t>
+          <t>156717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>336790</t>
+          <t>328409</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316599</t>
+          <t>310770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>352568</t>
+          <t>341334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444841</t>
+          <t>421002</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444841</t>
+          <t>421002</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444841</t>
+          <t>421002</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41161</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64326</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55342</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>118431</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44587</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70521</t>
+          <t>61435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>87695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185016</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115986</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>104015</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127180</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>109015</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67655</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130744</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>58,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128363</t>
+          <t>104511</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114765</t>
+          <t>93902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140699</t>
+          <t>114480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>237378</t>
+          <t>220497</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>186356</t>
+          <t>203292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261364</t>
+          <t>235983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>186086</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186086</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186086</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155337</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371372</t>
+          <t>323678</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371372</t>
+          <t>323678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371372</t>
+          <t>323678</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,107 +7593,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24443</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40196</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23275</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>39169</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>29723</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22864</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38314</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>22,92%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>61240</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>50035</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>72443</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>18,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33809</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25785</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>44740</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>64371</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>53060</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>77008</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -7706,107 +7706,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137859</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>129180</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>144933</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>137401</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>128793</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144687</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>137422</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>128831</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>144281</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>77,08%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>86,32%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>275281</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>264078</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>286486</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>81,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>147429</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>136498</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>155453</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>75,31%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>284830</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>272193</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>296141</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>143688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>185319</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>147455</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>245221</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160032</t>
+          <t>125557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206571</t>
+          <t>161697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324265</t>
+          <t>282577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>426090</t>
+          <t>337946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>535261</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>514894</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>556525</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>715</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>484126</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>416620</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>514386</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>579064</t>
+          <t>484974</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554694</t>
+          <t>466269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>601233</t>
+          <t>502409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1063190</t>
+          <t>1020235</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997016</t>
+          <t>990233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1098841</t>
+          <t>1045602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700213</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>661841</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>661841</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>661841</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627966</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761265</t>
+          <t>627966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1423106</t>
+          <t>1328179</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1423106</t>
+          <t>1328179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1423106</t>
+          <t>1328179</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
